--- a/esempi/orari-limbiate.xlsx
+++ b/esempi/orari-limbiate.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="75">
   <si>
     <t>Settimana 47</t>
   </si>
@@ -631,26 +631,110 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="4:34" x14ac:dyDescent="0.25">
+    <row r="3" spans="4:38" x14ac:dyDescent="0.25">
       <c r="D3" t="s">
         <v>4</v>
       </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" t="s">
+        <v>4</v>
+      </c>
       <c r="I3" t="s">
         <v>5</v>
       </c>
+      <c r="J3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M3" t="s">
+        <v>5</v>
+      </c>
       <c r="N3" t="s">
         <v>6</v>
       </c>
+      <c r="O3" t="s">
+        <v>6</v>
+      </c>
+      <c r="P3" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>6</v>
+      </c>
+      <c r="R3" t="s">
+        <v>6</v>
+      </c>
       <c r="S3" t="s">
         <v>7</v>
       </c>
+      <c r="T3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U3" t="s">
+        <v>7</v>
+      </c>
+      <c r="V3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W3" t="s">
+        <v>7</v>
+      </c>
       <c r="X3" t="s">
         <v>8</v>
       </c>
+      <c r="Y3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>8</v>
+      </c>
       <c r="AC3" t="s">
         <v>9</v>
       </c>
+      <c r="AD3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>9</v>
+      </c>
       <c r="AH3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL3" t="s">
         <v>10</v>
       </c>
     </row>
